--- a/intake_template.xlsx
+++ b/intake_template.xlsx
@@ -39,15 +39,15 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Courier New"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B4D3E"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How to use this intake template</t>
+          <t>This workbook is a PLANNING AID, not an input file</t>
         </is>
       </c>
     </row>
@@ -540,139 +540,187 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Pick the tab that matches your assay (Bulk RNA-seq, TAGseq, or sRNA-seq).</t>
+          <t>Nothing reads this file. It exists so you can think through, and write</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. Fill in the YELLOW cells (required). Optional cells are light gray.</t>
+          <t>down, every decision the pipeline will ask you about, before you start a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3. For any question you're not sure about, choose 'don't know' from the dropdown.</t>
+          <t>run. You then type those answers into the prompts.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   The pipeline can run a small probe job to figure it out for you.</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>4. Save the file as 'intake.xlsx' inside your project folder on FARM:</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>How to actually start a run</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       ~/new_project_inbox/&lt;your_project_name&gt;/intake.xlsx</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1. Fill in the tab that matches your assay, for your own reference.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5. Run one command on FARM:</t>
+          <t>2. From your Mac, upload the metadata spreadsheet and start the wizard:</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       ./scripts/run_from_intake.sh &lt;your_project_name&gt;</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       scripts/start_new.sh &lt;project_name&gt; &lt;metadata_file&gt; [fastq_dir]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6. Read the plan it prints. Type 'y' to launch.</t>
+          <t xml:space="preserve">   That drops you into an interactive session on FARM running</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       scripts/new_project.sh &lt;project_name&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Tips</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   which auto-detects the sample-ID and factor columns from the</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- Use the Help column on the right of each question for examples.</t>
+          <t xml:space="preserve">   metadata file and prompts you for the rest.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- Only fill in ONE tab per project. Leave the other tabs empty.</t>
+          <t>3. Read the plan it prints. Type 'y' to launch.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>- You can edit the questions themselves: see config/intake_questions.yaml.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>- If you change the questions, re-run scripts/generate_intake_template.py.</t>
+          <t>Note: the metadata spreadsheet in step 2 is your OWN sample table</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(.xlsx/.csv/.tsv, one row per sample). It is not this workbook.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>What 'probe' means</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Some questions (like strandedness or library type) can be answered by the</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tips</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>computer instead of you. If you choose 'don't know', the system runs a tiny</t>
+          <t>- Use the Help column on the right of each question for examples.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>(~5 minute) Salmon job on your probe sample and figures it out automatically.</t>
+          <t>- Only fill in ONE tab per project. Leave the other tabs empty.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>That's the 'probe' step. You can disable it and use defaults if you prefer.</t>
+          <t>- You can edit the questions themselves: see config/intake_questions.yaml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>- If you change the questions, re-run scripts/generate_intake_template.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Questions marked 'don't know'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Strandedness and library type do not have to be answered by you: Salmon</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>auto-detects the library type during quantification, and the pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>records what it found and warns you if it disagrees with what you</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>declared in config (samples.expected_libtype).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>There is no separate probe job; detection happens inside the normal run.</t>
         </is>
       </c>
     </row>
@@ -682,485 +730,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Bulk RNA-seq</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Standard mRNA-seq for differential expression.
-Choose this tab if your library is polyA-selected OR ribodepletion.
-Reads can be single-end or paired-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Q#</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Your answer</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Help / example</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Project name</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Folder name. Letters, numbers, underscores only. Example: chickpea_drought_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Contact email</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Where SLURM job notifications go. Example: yourname@ucdavis.edu</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Biological question (one sentence)</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Used in the Methods paragraph. Example: How does drought affect root transcriptome at 0/3/6 hours?</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Organism</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Common name, scientific name, or NCBI taxID. Examples: chickpea, Cicer arietinum, 3827</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="35" customHeight="1">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Tissue type</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Example: leaf, root, blood, tumor. Used in Methods paragraph + plant-vs-animal QC thresholds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="35" customHeight="1">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Sequencing platform</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Determines fastp poly-G trimming and read-length defaults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="35" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Primary comparison — which column in your metadata file?</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Example: treatment, timepoint, genotype. This is what DE contrasts pivot around.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="35" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Smallest group size (how many biological replicates in your smallest condition?)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Drives DE backend choice. 3 = minimum; 5+ much better; 12+ for subtle effects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="35" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Same subject measured at multiple timepoints / conditions?</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Yes = adds random effect (DREAM). No = standard limma-voom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="35" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Known batch column to model? (sequencing date, library prep batch, etc.)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Type the column name from your metadata file, or 'none' if no known batches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="35" customHeight="1">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>FASTQ folder path (on FARM)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Full path. Example: /group/kliebengrp/yourname/projects/myproject/fastq</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="35" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Metadata file (CSV or Excel) — full path on FARM</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>One row per sample. Must contain a sample-ID column and your primary_factor column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="35" customHeight="1">
-      <c r="A17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Sample-ID column name in your metadata file</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>The column that holds sample names matching the FASTQ filenames. Example: Sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="35" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Probe sample (which sample_id should the system use for probe runs?)</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Used for 'don't know' answers — a single clean sample to detect strandedness, library type, etc. Leave blank to auto-pick the first sample in metadata.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="35" customHeight="1">
-      <c r="A19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Run probes for any 'don't know' answers?</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Yes = run small SLURM jobs to detect missing info (recommended). No = use conservative defaults, you can re-run later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="35" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Run functional enrichment (GO + KEGG)?</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="35" customHeight="1">
-      <c r="A21" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>How should the system get the OrgDb (for GO enrichment)?</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="35" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Where should built OrgDb packages be cached?</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>~/orgdb_cache</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="35" customHeight="1">
-      <c r="A23" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Run WGCNA co-expression network?</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="35" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Library prep type</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>polyA = standard mRNA (default for healthy eukaryotic samples). ribodepletion = preserves all RNA classes including lncRNA, pre-mRNA, viral RNA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Read configuration</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Look at your FASTQ files: if you have R1 and R2 per sample, it's paired-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Strandedness</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>reverse</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Modern kits (NEBNext Ultra II Directional, TruSeq Stranded) are reverse-stranded. Pre-2015 kits are usually unstranded.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <dataValidations count="9">
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NovaSeq,NextSeq,MiSeq,Other Illumina,don't know"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"auto,force_build,use_existing,skip"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"polyA mRNA-seq,ribodepletion,don't know"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"paired-end,single-end,don't know"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"reverse,forward,unstranded,don't know"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1178,16 +747,16 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>TAGseq</t>
+          <t>Bulk RNA-seq</t>
         </is>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>3'-tag RNA-seq (QuantSeq, Lexogen). Single-end, short reads (~5-10M),
-sequences only the 3' end of each polyadenylated transcript.
-Good for large-cohort DE studies. NOT for splicing or isoforms.</t>
+          <t>Standard mRNA-seq for differential expression.
+Choose this tab if your library is polyA-selected OR ribodepletion.
+Reads can be single-end or paired-end.</t>
         </is>
       </c>
     </row>
@@ -1439,13 +1008,13 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Probe sample (which sample_id should the system use for probe runs?)</t>
+          <t>Expected library type, if you know it (e.g. ISR, SR, U)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Used for 'don't know' answers — a single clean sample to detect strandedness, library type, etc. Leave blank to auto-pick the first sample in metadata.</t>
+          <t>Optional. Salmon detects the library type itself during quantification; giving it here makes the pipeline warn you if the detected value disagrees. Leave blank to accept whatever Salmon finds.</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1024,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Run probes for any 'don't know' answers?</t>
+          <t>Run functional enrichment (GO + KEGG)?</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1465,7 +1034,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Yes = run small SLURM jobs to detect missing info (recommended). No = use conservative defaults, you can re-run later.</t>
+          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
         </is>
       </c>
     </row>
@@ -1475,17 +1044,17 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Run functional enrichment (GO + KEGG)?</t>
+          <t>How should the system get the OrgDb (for GO enrichment)?</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
+          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
         </is>
       </c>
     </row>
@@ -1495,17 +1064,17 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>How should the system get the OrgDb (for GO enrichment)?</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>auto</t>
+          <t>Where should built OrgDb packages be cached?</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>~/orgdb_cache</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
+          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
         </is>
       </c>
     </row>
@@ -1515,17 +1084,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Where should built OrgDb packages be cached?</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>~/orgdb_cache</t>
+          <t>Run WGCNA co-expression network?</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
+          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
         </is>
       </c>
     </row>
@@ -1535,17 +1104,13 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Run WGCNA co-expression network?</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Library prep type</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
+          <t>polyA = standard mRNA (default for healthy eukaryotic samples). ribodepletion = preserves all RNA classes including lncRNA, pre-mRNA, viral RNA.</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1120,13 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Library prep kit</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Lexogen QuantSeq FWD</t>
-        </is>
-      </c>
+          <t>Read configuration</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr"/>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Most common is QuantSeq FWD from Lexogen.</t>
+          <t>Look at your FASTQ files: if you have R1 and R2 per sample, it's paired-end.</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1136,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Strandedness (TAGseq is almost always reverse-stranded)</t>
+          <t>Strandedness</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1585,7 +1146,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>QuantSeq FWD = forward-stranded; QuantSeq REV = reverse. Leave as default if you don't know.</t>
+          <t>Modern kits (NEBNext Ultra II Directional, TruSeq Stranded) are reverse-stranded. Pre-2015 kits are usually unstranded.</t>
         </is>
       </c>
     </row>
@@ -1605,18 +1166,459 @@
       <formula1>"yes,no"</formula1>
     </dataValidation>
     <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"auto,force_build,use_existing,skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"polyA mRNA-seq,ribodepletion,don't know"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"paired-end,single-end,don't know"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"reverse,forward,unstranded,don't know"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>TAGseq</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>3'-tag RNA-seq (QuantSeq, Lexogen). Single-end, short reads (~5-10M),
+sequences only the 3' end of each polyadenylated transcript.
+Good for large-cohort DE studies. NOT for splicing or isoforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Your answer</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Help / example</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Project name</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Folder name. Letters, numbers, underscores only. Example: chickpea_drought_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Contact email</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Where SLURM job notifications go. Example: yourname@ucdavis.edu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Biological question (one sentence)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Used in the Methods paragraph. Example: How does drought affect root transcriptome at 0/3/6 hours?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Organism</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Common name, scientific name, or NCBI taxID. Examples: chickpea, Cicer arietinum, 3827</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Tissue type</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Example: leaf, root, blood, tumor. Used in Methods paragraph + plant-vs-animal QC thresholds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Sequencing platform</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Determines fastp poly-G trimming and read-length defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Primary comparison — which column in your metadata file?</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Example: treatment, timepoint, genotype. This is what DE contrasts pivot around.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="35" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Smallest group size (how many biological replicates in your smallest condition?)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Drives DE backend choice. 3 = minimum; 5+ much better; 12+ for subtle effects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Same subject measured at multiple timepoints / conditions?</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Yes = adds random effect (DREAM). No = standard limma-voom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Known batch column to model? (sequencing date, library prep batch, etc.)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Type the column name from your metadata file, or 'none' if no known batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>FASTQ folder path (on FARM)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Full path. Example: /group/kliebengrp/yourname/projects/myproject/fastq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Metadata file (CSV or Excel) — full path on FARM</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>One row per sample. Must contain a sample-ID column and your primary_factor column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Sample-ID column name in your metadata file</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>The column that holds sample names matching the FASTQ filenames. Example: Sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Expected library type, if you know it (e.g. ISR, SR, U)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Optional. Salmon detects the library type itself during quantification; giving it here makes the pipeline warn you if the detected value disagrees. Leave blank to accept whatever Salmon finds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Run functional enrichment (GO + KEGG)?</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>How should the system get the OrgDb (for GO enrichment)?</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Where should built OrgDb packages be cached?</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>~/orgdb_cache</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Run WGCNA co-expression network?</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Library prep kit</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Lexogen QuantSeq FWD</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Most common is QuantSeq FWD from Lexogen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Strandedness (TAGseq is almost always reverse-stranded)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>QuantSeq FWD = forward-stranded; QuantSeq REV = reverse. Leave as default if you don't know.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="7">
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NovaSeq,NextSeq,MiSeq,Other Illumina,don't know"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"auto,force_build,use_existing,skip"</formula1>
     </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
     <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
+      <formula1>"Lexogen QuantSeq FWD,Lexogen QuantSeq REV,other,don't know"</formula1>
     </dataValidation>
     <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Lexogen QuantSeq FWD,Lexogen QuantSeq REV,other,don't know"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"reverse,forward,don't know"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1630,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1903,13 +1905,13 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Probe sample (which sample_id should the system use for probe runs?)</t>
+          <t>Expected library type, if you know it (e.g. ISR, SR, U)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Used for 'don't know' answers — a single clean sample to detect strandedness, library type, etc. Leave blank to auto-pick the first sample in metadata.</t>
+          <t>Optional. Salmon detects the library type itself during quantification; giving it here makes the pipeline warn you if the detected value disagrees. Leave blank to accept whatever Salmon finds.</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1921,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Run probes for any 'don't know' answers?</t>
+          <t>Run functional enrichment (GO + KEGG)?</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1929,7 +1931,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Yes = run small SLURM jobs to detect missing info (recommended). No = use conservative defaults, you can re-run later.</t>
+          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
         </is>
       </c>
     </row>
@@ -1939,17 +1941,17 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Run functional enrichment (GO + KEGG)?</t>
+          <t>How should the system get the OrgDb (for GO enrichment)?</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Yes adds Stage 4. Auto-skipped if OrgDb / KEGG code unavailable.</t>
+          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
         </is>
       </c>
     </row>
@@ -1959,17 +1961,17 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>How should the system get the OrgDb (for GO enrichment)?</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>auto</t>
+          <t>Where should built OrgDb packages be cached?</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>~/orgdb_cache</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>auto = try Bioconductor → cache → NCBI Gene → eggNOG-mapper (in order). force_build = always rebuild from reference (slow, ~2 hr, works for any genome). use_existing = name a Bioconductor package below. skip = no enrichment.</t>
+          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
         </is>
       </c>
     </row>
@@ -1979,17 +1981,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Where should built OrgDb packages be cached?</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>~/orgdb_cache</t>
+          <t>Run WGCNA co-expression network?</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Full path on FARM. Default ~/orgdb_cache/ is fine and per-user. For a lab-shared cache, use /group/&lt;lab&gt;/orgdb_cache/. Leave blank for default.</t>
+          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
         </is>
       </c>
     </row>
@@ -1999,17 +2001,13 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Run WGCNA co-expression network?</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Small-RNA library kit (determines adapter sequence)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Yes adds Stage 5. Auto-skipped if total samples &lt; 15 (unreliable below that).</t>
+          <t>NEXTflex v4 is the plant sRNA standard (reduces ligation bias). NEBNext is more biased but cheaper.</t>
         </is>
       </c>
     </row>
@@ -2019,31 +2017,15 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Small-RNA library kit (determines adapter sequence)</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr"/>
+          <t>Expected sRNA size range (nt)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>18-30 (broad)</t>
+        </is>
+      </c>
       <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>NEXTflex v4 is the plant sRNA standard (reduces ligation bias). NEBNext is more biased but cheaper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Expected sRNA size range (nt)</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>18-30 (broad)</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>miRNAs = 20-22 nt; plant siRNAs = 21-24 nt; full sRNA universe = 18-30 nt.</t>
         </is>
@@ -2054,7 +2036,7 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="8">
+  <dataValidations count="7">
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NovaSeq,NextSeq,MiSeq,Other Illumina,don't know"</formula1>
     </dataValidation>
@@ -2065,18 +2047,15 @@
       <formula1>"yes,no"</formula1>
     </dataValidation>
     <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"auto,force_build,use_existing,skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"auto,force_build,use_existing,skip"</formula1>
-    </dataValidation>
     <dataValidation sqref="C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
+      <formula1>"NEXTflex Small RNA v4,NEBNext Multiplex Small RNA,QIAseq miRNA,don't know"</formula1>
     </dataValidation>
     <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NEXTflex Small RNA v4,NEBNext Multiplex Small RNA,QIAseq miRNA,don't know"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"18-30 (broad),20-22 (miRNA-focused),21-24 (plant siRNA)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/intake_template.xlsx
+++ b/intake_template.xlsx
@@ -810,7 +810,7 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Where SLURM job notifications go. Example: yourname@ucdavis.edu</t>
+          <t>Where SLURM job notifications go. Example: you@example.edu</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Where SLURM job notifications go. Example: yourname@ucdavis.edu</t>
+          <t>Where SLURM job notifications go. Example: you@example.edu</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Where SLURM job notifications go. Example: yourname@ucdavis.edu</t>
+          <t>Where SLURM job notifications go. Example: you@example.edu</t>
         </is>
       </c>
     </row>

--- a/intake_template.xlsx
+++ b/intake_template.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re2ab5c6d1a9c426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk RNA-seq" sheetId="2" r:id="R2e7c11f3cabd4af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAGseq" sheetId="3" r:id="R1c7e1463cb6f45a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sRNA-seq" sheetId="4" r:id="Rd75b59d1e68a4cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="5" r:id="Ra74a2a8ba39d4008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Libraries" sheetId="6" r:id="Rafa898603ad7442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reads" sheetId="7" r:id="Re4976f2dea80472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R52182935ba874c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk RNA-seq" sheetId="2" r:id="Rcd36cd2ef9934461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAGseq" sheetId="3" r:id="R02685295f5d746c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sRNA-seq" sheetId="4" r:id="Rc85db9ae5f5744a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="5" r:id="R06a01f7a5a3140ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Libraries" sheetId="6" r:id="R67d8b9055e90469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reads" sheetId="7" r:id="R0a54bcb5d2d44fc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -106,8 +106,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -164,6 +169,11 @@
         <x:fgColor rgb="FF2E7D32"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F5F5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -185,7 +195,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -357,6 +367,25 @@
     <x:xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -661,7 +690,7 @@
         <x:v>Template schema version</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -674,7 +703,7 @@
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="48" t="str">
-        <x:v>Current execution: annotated, non-UMI bulk gene expression and differential expression; independent groups, optionally including a batch column.</x:v>
+        <x:v>Current execution: annotated, non-UMI bulk gene expression and differential expression; Salmon or STAR, explicit fixed-effect methods, independent groups with optional batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -739,12 +768,12 @@
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="48" t="str">
-        <x:v>The current model compares all levels of the primary factor. Advanced contrasts, subject effects, reference overrides and execution settings still require configuration outside this workbook.</x:v>
+        <x:v>Bulk method, custom references and basic preprocessing have input fields. Advanced contrasts, subject effects, analysis objectives and executor settings still require configuration outside this workbook.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="48" t="str">
-        <x:v>Blank strandedness knowledge is not a reverse-stranded assumption: choose don't know. Salmon detects library type and reports disagreement with declared expectations.</x:v>
+        <x:v>Blank strandedness knowledge is not a reverse-stranded assumption: choose don't know. Salmon detects library type and reports disagreement. STAR requires a known declared strand; it does not infer strand.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -1235,12 +1264,172 @@
         <x:v>library_kit</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="51" customHeight="1">
+      <x:c r="A30" s="66" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B30" s="66" t="str">
+        <x:v>Bulk quantification method</x:v>
+      </x:c>
+      <x:c r="C30" s="68" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="D30" s="20" t="str">
+        <x:v>auto selects Salmon for gene expression. STAR needs a compatible genome/GTF and known strand.</x:v>
+      </x:c>
+      <x:c r="E30" s="39" t="str">
+        <x:v>analysis_quantifier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="51" customHeight="1">
+      <x:c r="A31" s="66" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B31" s="66" t="str">
+        <x:v>Differential expression method</x:v>
+      </x:c>
+      <x:c r="C31" s="68" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="D31" s="20" t="str">
+        <x:v>auto selects limma-voom for this independent design. Explicit methods keep the declared model.</x:v>
+      </x:c>
+      <x:c r="E31" s="39" t="str">
+        <x:v>analysis_backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="51" customHeight="1">
+      <x:c r="A32" s="66" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B32" s="66" t="str">
+        <x:v>Custom genome FASTA path or URL</x:v>
+      </x:c>
+      <x:c r="C32" s="68"/>
+      <x:c r="D32" s="20" t="str">
+        <x:v>Optional custom reference set. With STAR, provide genome and GTF. With Salmon genomic decoys, also provide transcripts.</x:v>
+      </x:c>
+      <x:c r="E32" s="39" t="str">
+        <x:v>reference_genome</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="51" customHeight="1">
+      <x:c r="A33" s="66" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B33" s="66" t="str">
+        <x:v>Custom transcriptome FASTA path or URL</x:v>
+      </x:c>
+      <x:c r="C33" s="68"/>
+      <x:c r="D33" s="20" t="str">
+        <x:v>Salmon custom reference requires transcripts and GTF; genomic decoys additionally need genome. IDs must match annotation.</x:v>
+      </x:c>
+      <x:c r="E33" s="39" t="str">
+        <x:v>reference_transcriptome</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="51" customHeight="1">
+      <x:c r="A34" s="66" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B34" s="66" t="str">
+        <x:v>Custom annotation GTF path or URL</x:v>
+      </x:c>
+      <x:c r="C34" s="68"/>
+      <x:c r="D34" s="20" t="str">
+        <x:v>Use the matching assembly/release. If any custom reference is supplied, provide the complete required set.</x:v>
+      </x:c>
+      <x:c r="E34" s="39" t="str">
+        <x:v>reference_gtf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="51" customHeight="1">
+      <x:c r="A35" s="66" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B35" s="66" t="str">
+        <x:v>Salmon decoy profile</x:v>
+      </x:c>
+      <x:c r="C35" s="68" t="str">
+        <x:v>genome</x:v>
+      </x:c>
+      <x:c r="D35" s="20" t="str">
+        <x:v>genome is the new-project default. transcriptome only explicitly disables decoys. STAR does not use this setting.</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="str">
+        <x:v>reference_decoys</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="51" customHeight="1">
+      <x:c r="A36" s="66" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B36" s="66" t="str">
+        <x:v>Poly-G trimming</x:v>
+      </x:c>
+      <x:c r="C36" s="68" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="D36" s="20" t="str">
+        <x:v>auto uses fastp instrument-header detection. Choose on or off when the library protocol requires it.</x:v>
+      </x:c>
+      <x:c r="E36" s="39" t="str">
+        <x:v>preprocess_poly_g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="51" customHeight="1">
+      <x:c r="A37" s="66" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B37" s="66" t="str">
+        <x:v>Explicit R1 adapter sequence</x:v>
+      </x:c>
+      <x:c r="C37" s="68"/>
+      <x:c r="D37" s="20" t="str">
+        <x:v>Optional A/C/G/T sequence. Blank uses the bulk processor auto-detection. Kit-specific processing is not implied.</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="str">
+        <x:v>preprocess_adapter_r1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="51" customHeight="1">
+      <x:c r="A38" s="66" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B38" s="66" t="str">
+        <x:v>Explicit R2 adapter sequence</x:v>
+      </x:c>
+      <x:c r="C38" s="68"/>
+      <x:c r="D38" s="20" t="str">
+        <x:v>Paired reads only; also supply R1 adapter. Blank uses the R1 sequence when R1 is explicit.</x:v>
+      </x:c>
+      <x:c r="E38" s="39" t="str">
+        <x:v>preprocess_adapter_r2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="51" customHeight="1">
+      <x:c r="A39" s="66" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B39" s="66" t="str">
+        <x:v>Minimum retained read length (nt)</x:v>
+      </x:c>
+      <x:c r="C39" s="69" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D39" s="20" t="str">
+        <x:v>Bulk minimum after processing. This is not a small-RNA size-selection profile.</x:v>
+      </x:c>
+      <x:c r="E39" s="39" t="str">
+        <x:v>preprocess_minimum_length</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
-  <x:dataValidations count="15">
+  <x:dataValidations count="20">
     <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="C10">
       <x:formula1>"NovaSeq,NextSeq,MiSeq,Other Illumina,don't know"</x:formula1>
     </x:dataValidation>
@@ -1285,6 +1474,22 @@
     </x:dataValidation>
     <x:dataValidation type="list" sqref="C28">
       <x:formula1>"no,yes,don't know"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C30">
+      <x:formula1>"auto,salmon,star"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C31">
+      <x:formula1>"auto,limma_voom,edger_ql,deseq2"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C35">
+      <x:formula1>"genome,transcriptome only"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C36">
+      <x:formula1>"auto,on,off"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="C39">
+      <x:formula1>1</x:formula1>
+      <x:formula2>10000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/intake_template.xlsx
+++ b/intake_template.xlsx
@@ -680,7 +680,7 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Full intake and route coverage remains incomplete. See docs/INTAKE_TEMPLATE_AUDIT.md for required fields, implementation gaps and the v2 publication gate.</t>
+          <t>Only the Bulk RNA-seq tab can be run in this release. The other assay tabs are for planning.</t>
         </is>
       </c>
     </row>
